--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.58000334173582</v>
+        <v>9.356750543032071</v>
       </c>
       <c r="D2" t="n">
-        <v>56.27694596662796</v>
+        <v>9.145003719577044</v>
       </c>
       <c r="E2" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F2" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.57926679175876</v>
+        <v>8.056630853660797</v>
       </c>
       <c r="D3" t="n">
-        <v>44.92963274995535</v>
+        <v>7.301065321867743</v>
       </c>
       <c r="E3" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F3" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.69725455446472</v>
+        <v>8.563303865100517</v>
       </c>
       <c r="D4" t="n">
-        <v>9.598563713475549</v>
+        <v>1.559766603439777</v>
       </c>
       <c r="E4" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F4" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.26095608513165</v>
+        <v>7.679905363833893</v>
       </c>
       <c r="D5" t="n">
-        <v>7.128546714167886</v>
+        <v>1.158388841052282</v>
       </c>
       <c r="E5" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F5" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.81280674955607</v>
+        <v>8.582081096802861</v>
       </c>
       <c r="D6" t="n">
-        <v>12.10882861458332</v>
+        <v>1.967684649869789</v>
       </c>
       <c r="E6" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F6" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.51411345073407</v>
+        <v>5.608543435744286</v>
       </c>
       <c r="D7" t="n">
-        <v>25.99302449491529</v>
+        <v>4.223866480423736</v>
       </c>
       <c r="E7" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F7" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>71.47352292267286</v>
+        <v>11.61444747493434</v>
       </c>
       <c r="D8" t="n">
-        <v>72.50498123266948</v>
+        <v>11.78205945030879</v>
       </c>
       <c r="E8" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F8" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90864960182759</v>
+        <v>9.897655560296984</v>
       </c>
       <c r="D9" t="n">
-        <v>27.82827926976506</v>
+        <v>4.522095381336822</v>
       </c>
       <c r="E9" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F9" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.79911119664507</v>
+        <v>8.742355569454825</v>
       </c>
       <c r="D10" t="n">
-        <v>32.95871906193799</v>
+        <v>5.355791847564924</v>
       </c>
       <c r="E10" t="n">
-        <v>9.489555160671216</v>
+        <v>1.542052713609073</v>
       </c>
       <c r="F10" t="n">
-        <v>20.99598264914784</v>
+        <v>3.411847180486523</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
